--- a/outputs/57743.xlsx
+++ b/outputs/57743.xlsx
@@ -232,24 +232,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,291 +449,291 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="10.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A2,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A3,C:C,0)),"")</f>
         <v>312.625</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="str">
+      <c r="B4" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A4,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="str">
+      <c r="B5" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A5,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="str">
+      <c r="B6" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A6,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="str">
+      <c r="B7" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A7,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>386</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A8,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>418</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A9,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="2" t="n">
         <v>468</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="str">
+      <c r="B10" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A10,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <v>488</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="3" t="str">
+      <c r="B11" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A11,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="2" t="n">
         <v>55.35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="str">
+      <c r="B12" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A12,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="2" t="n">
         <v>71.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="3" t="str">
+      <c r="B13" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A13,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="2" t="n">
         <v>55.35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3" t="str">
+      <c r="B14" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A14,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="2" t="n">
         <v>55.35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A15,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="2" t="n">
         <v>53.3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A16,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="2" t="n">
         <v>53.3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="3" t="str">
+      <c r="B17" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A17,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="2" t="n">
         <v>56.375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="str">
+      <c r="B18" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A18,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="2" t="n">
         <v>59.45</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="str">
+      <c r="B19" s="4" t="str">
         <f aca="false">IFERROR(INDEX(D:D,MATCH(A19,C:C,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="2" t="n">
         <v>312.625</v>
       </c>
     </row>

--- a/outputs/57743.xlsx
+++ b/outputs/57743.xlsx
@@ -471,10 +471,7 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A2,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
@@ -486,10 +483,7 @@
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A3,C:C,0)),"")</f>
-        <v>312.625</v>
-      </c>
+      <c r="B3" s="4"/>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
@@ -501,10 +495,7 @@
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A4,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
@@ -516,10 +507,7 @@
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A5,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B5" s="4"/>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
@@ -531,10 +519,7 @@
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A6,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
@@ -546,10 +531,7 @@
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A7,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B7" s="4"/>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
@@ -561,10 +543,7 @@
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A8,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B8" s="4"/>
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
@@ -576,10 +555,7 @@
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A9,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B9" s="4"/>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
@@ -591,10 +567,7 @@
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A10,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
@@ -606,10 +579,7 @@
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A11,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B11" s="4"/>
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
@@ -621,10 +591,7 @@
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A12,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
@@ -636,10 +603,7 @@
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A13,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B13" s="4"/>
       <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
@@ -651,10 +615,7 @@
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A14,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="1" t="s">
         <v>28</v>
       </c>
@@ -666,10 +627,7 @@
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A15,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B15" s="4"/>
       <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
@@ -681,10 +639,7 @@
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A16,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B16" s="4"/>
       <c r="C16" s="1" t="s">
         <v>32</v>
       </c>
@@ -696,10 +651,7 @@
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A17,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B17" s="4"/>
       <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
@@ -711,10 +663,7 @@
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A18,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B18" s="4"/>
       <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
@@ -726,10 +675,7 @@
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="4" t="str">
-        <f aca="false">IFERROR(INDEX(D:D,MATCH(A19,C:C,0)),"")</f>
-        <v/>
-      </c>
+      <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
         <v>5</v>
       </c>
